--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>330070</t>
+          <t>330859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392177</t>
+          <t>393521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>650822</t>
+          <t>647962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>724565</t>
+          <t>723848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>994354</t>
+          <t>998082</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1092043</t>
+          <t>1097319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>582466</t>
+          <t>581122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>644573</t>
+          <t>643784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>613232</t>
+          <t>613949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686975</t>
+          <t>689835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1220397</t>
+          <t>1215121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1318086</t>
+          <t>1314358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164646</t>
+          <t>162378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221259</t>
+          <t>221519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>268600</t>
+          <t>268372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>334263</t>
+          <t>338673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>452541</t>
+          <t>449273</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>536970</t>
+          <t>538521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1742698</t>
+          <t>1742438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1799311</t>
+          <t>1801579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1423540</t>
+          <t>1419130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1489203</t>
+          <t>1489431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3184790</t>
+          <t>3183239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3269219</t>
+          <t>3272487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21144</t>
+          <t>19974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45759</t>
+          <t>44491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36786</t>
+          <t>37024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66976</t>
+          <t>64604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62211</t>
+          <t>64118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100533</t>
+          <t>100142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>435422</t>
+          <t>436690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>460037</t>
+          <t>461207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391655</t>
+          <t>394027</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>421845</t>
+          <t>421607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>839280</t>
+          <t>839671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877602</t>
+          <t>875695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>535487</t>
+          <t>542033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>630046</t>
+          <t>629397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>985003</t>
+          <t>983763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1092650</t>
+          <t>1098936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1546474</t>
+          <t>1545084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1691601</t>
+          <t>1687739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2789736</t>
+          <t>2790385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2884295</t>
+          <t>2877749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2461580</t>
+          <t>2455294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2569227</t>
+          <t>2570467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5282411</t>
+          <t>5286273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5427538</t>
+          <t>5428928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>203357</t>
+          <t>203125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253316</t>
+          <t>254452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>450852</t>
+          <t>453026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>516961</t>
+          <t>519795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>671092</t>
+          <t>670709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>755277</t>
+          <t>753590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>501031</t>
+          <t>499895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>550990</t>
+          <t>551222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>477699</t>
+          <t>474865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>543808</t>
+          <t>541634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>993730</t>
+          <t>995417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1077915</t>
+          <t>1078298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>201364</t>
+          <t>202205</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258857</t>
+          <t>258133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>335687</t>
+          <t>335484</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>409628</t>
+          <t>403811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>550364</t>
+          <t>553112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>647759</t>
+          <t>646069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1817528</t>
+          <t>1818252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1875021</t>
+          <t>1874180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1578672</t>
+          <t>1584489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1652613</t>
+          <t>1652816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3416926</t>
+          <t>3418616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3514321</t>
+          <t>3511573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,39%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34596</t>
+          <t>36996</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64097</t>
+          <t>67604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43941</t>
+          <t>43959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73006</t>
+          <t>75388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86729</t>
+          <t>87148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126725</t>
+          <t>126539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>482789</t>
+          <t>479282</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512290</t>
+          <t>509890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>476134</t>
+          <t>473752</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>505199</t>
+          <t>505181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>969302</t>
+          <t>969488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1009298</t>
+          <t>1008879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>462995</t>
+          <t>466016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>545959</t>
+          <t>547010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>857823</t>
+          <t>856190</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>970431</t>
+          <t>965757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1343710</t>
+          <t>1339408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1488955</t>
+          <t>1483391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2831659</t>
+          <t>2830608</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2914623</t>
+          <t>2911602</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2561669</t>
+          <t>2566343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2674277</t>
+          <t>2675910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5420763</t>
+          <t>5426327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5566008</t>
+          <t>5570310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168756</t>
+          <t>169410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>209468</t>
+          <t>209626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>421938</t>
+          <t>420877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>463527</t>
+          <t>462181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>601859</t>
+          <t>599037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>664351</t>
+          <t>659220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305470</t>
+          <t>305312</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346182</t>
+          <t>345528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291981</t>
+          <t>293327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333570</t>
+          <t>334631</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>606095</t>
+          <t>611226</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>668587</t>
+          <t>671409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>225283</t>
+          <t>219017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>376658</t>
+          <t>376109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>370787</t>
+          <t>383581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>580495</t>
+          <t>580545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>654392</t>
+          <t>665315</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>932004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1913669</t>
+          <t>1914218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2065044</t>
+          <t>2071310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1657328</t>
+          <t>1657278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1867036</t>
+          <t>1854242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3595940</t>
+          <t>3596146</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3873758</t>
+          <t>3862835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65044</t>
+          <t>66295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98890</t>
+          <t>98144</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129310</t>
+          <t>129592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165732</t>
+          <t>166089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205572</t>
+          <t>204456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253535</t>
+          <t>251963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>547733</t>
+          <t>548479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>581579</t>
+          <t>580328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>494731</t>
+          <t>494374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531153</t>
+          <t>530871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053551</t>
+          <t>1055123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1101514</t>
+          <t>1102630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>458049</t>
+          <t>455442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>662386</t>
+          <t>654938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>887446</t>
+          <t>894853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1188446</t>
+          <t>1191646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1476018</t>
+          <t>1449643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1817035</t>
+          <t>1820040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2789503</t>
+          <t>2796951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2993840</t>
+          <t>2996447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2465348</t>
+          <t>2462148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2766348</t>
+          <t>2758941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5288648</t>
+          <t>5285643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5629665</t>
+          <t>5656040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>330859</t>
+          <t>331637</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>393521</t>
+          <t>393956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>647962</t>
+          <t>650422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>723848</t>
+          <t>722662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>998082</t>
+          <t>997074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1097319</t>
+          <t>1095226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>581122</t>
+          <t>580687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>643784</t>
+          <t>643006</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>613949</t>
+          <t>615135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>689835</t>
+          <t>687375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1215121</t>
+          <t>1217214</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1314358</t>
+          <t>1315366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>162378</t>
+          <t>163728</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221519</t>
+          <t>218038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>268372</t>
+          <t>271295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>338673</t>
+          <t>339910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>449273</t>
+          <t>449025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>538521</t>
+          <t>535647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1742438</t>
+          <t>1745919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1801579</t>
+          <t>1800229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1419130</t>
+          <t>1417893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1489431</t>
+          <t>1486508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3183239</t>
+          <t>3186113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3272487</t>
+          <t>3272735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>19454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44491</t>
+          <t>43407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37024</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64604</t>
+          <t>66184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64118</t>
+          <t>63145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100142</t>
+          <t>99870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436690</t>
+          <t>437774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>461207</t>
+          <t>461727</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>394027</t>
+          <t>392447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>421607</t>
+          <t>421452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>839671</t>
+          <t>839943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>875695</t>
+          <t>876668</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>542033</t>
+          <t>535649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>629397</t>
+          <t>632557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>983763</t>
+          <t>984299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1098936</t>
+          <t>1094586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1545084</t>
+          <t>1550211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1687739</t>
+          <t>1689900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2790385</t>
+          <t>2787225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2877749</t>
+          <t>2884133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2455294</t>
+          <t>2459644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2570467</t>
+          <t>2569931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5286273</t>
+          <t>5284112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5428928</t>
+          <t>5423801</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>203125</t>
+          <t>202865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254452</t>
+          <t>250826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>453026</t>
+          <t>452410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>519795</t>
+          <t>518093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>670709</t>
+          <t>672582</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>753590</t>
+          <t>755756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>499895</t>
+          <t>503521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>551222</t>
+          <t>551482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>474865</t>
+          <t>476567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>541634</t>
+          <t>542250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>995417</t>
+          <t>993251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1078298</t>
+          <t>1076425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202205</t>
+          <t>199922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258133</t>
+          <t>259866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>335484</t>
+          <t>333090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>403811</t>
+          <t>406805</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>553112</t>
+          <t>546898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>646069</t>
+          <t>647583</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1818252</t>
+          <t>1816519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1874180</t>
+          <t>1876463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1584489</t>
+          <t>1581495</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1652816</t>
+          <t>1655210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3418616</t>
+          <t>3417102</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3511573</t>
+          <t>3517787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36996</t>
+          <t>36160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67604</t>
+          <t>64507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43959</t>
+          <t>43795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75388</t>
+          <t>72483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87148</t>
+          <t>87615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126539</t>
+          <t>129609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479282</t>
+          <t>482379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509890</t>
+          <t>510726</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>473752</t>
+          <t>476657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>505181</t>
+          <t>505345</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>969488</t>
+          <t>966418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1008879</t>
+          <t>1008412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>466016</t>
+          <t>465036</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>547010</t>
+          <t>548545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>856190</t>
+          <t>859304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>965757</t>
+          <t>969839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1339408</t>
+          <t>1354113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1483391</t>
+          <t>1489906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2830608</t>
+          <t>2829073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2911602</t>
+          <t>2912582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2566343</t>
+          <t>2562261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2675910</t>
+          <t>2672796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5426327</t>
+          <t>5419812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5570310</t>
+          <t>5555605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,4%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>189009</t>
+          <t>201389</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169410</t>
+          <t>180928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>209626</t>
+          <t>224048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>442456</t>
+          <t>474485</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>420877</t>
+          <t>453120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>462181</t>
+          <t>496925</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>631465</t>
+          <t>675875</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>599037</t>
+          <t>643339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>659220</t>
+          <t>709971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>50,69%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>325929</t>
+          <t>377140</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305312</t>
+          <t>354481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>345528</t>
+          <t>397601</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>313052</t>
+          <t>347553</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293327</t>
+          <t>325113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>334631</t>
+          <t>368918</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>638981</t>
+          <t>724692</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>611226</t>
+          <t>690596</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671409</t>
+          <t>757228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>324037</t>
+          <t>348842</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>219017</t>
+          <t>314669</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>376109</t>
+          <t>386286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>507111</t>
+          <t>565007</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>383581</t>
+          <t>530461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>580545</t>
+          <t>604506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>831148</t>
+          <t>913850</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>665315</t>
+          <t>862341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>932004</t>
+          <t>971056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1966290</t>
+          <t>1881724</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1914218</t>
+          <t>1844280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2071310</t>
+          <t>1915897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1730712</t>
+          <t>1606385</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1657278</t>
+          <t>1566886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1854242</t>
+          <t>1640931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3697002</t>
+          <t>3488109</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3596146</t>
+          <t>3430903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3862835</t>
+          <t>3539618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>80,41%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81429</t>
+          <t>90092</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66295</t>
+          <t>73039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98144</t>
+          <t>108638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>147890</t>
+          <t>167281</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129592</t>
+          <t>146891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166089</t>
+          <t>187223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>229320</t>
+          <t>257374</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204456</t>
+          <t>231490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>251963</t>
+          <t>289032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>565194</t>
+          <t>621495</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>548479</t>
+          <t>602949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>580328</t>
+          <t>638548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512573</t>
+          <t>567596</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>494374</t>
+          <t>547654</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>530871</t>
+          <t>587986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1077766</t>
+          <t>1189090</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1055123</t>
+          <t>1157432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1102630</t>
+          <t>1214974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>594475</t>
+          <t>640324</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>455442</t>
+          <t>592505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>654938</t>
+          <t>688425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1097458</t>
+          <t>1206774</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>894853</t>
+          <t>1157126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1191646</t>
+          <t>1255524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1691933</t>
+          <t>1847098</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1449643</t>
+          <t>1775895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1820040</t>
+          <t>1913625</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2857414</t>
+          <t>2880359</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2796951</t>
+          <t>2832258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2996447</t>
+          <t>2928178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2556336</t>
+          <t>2521533</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2462148</t>
+          <t>2472783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2758941</t>
+          <t>2571181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5413750</t>
+          <t>5401892</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5285643</t>
+          <t>5335365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5656040</t>
+          <t>5473095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>75,5%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
